--- a/data/raw/holdings-daily-us-en-xsd.xlsx
+++ b/data/raw/holdings-daily-us-en-xsd.xlsx
@@ -192,7 +192,7 @@
     <t>XSD</t>
   </si>
   <si>
-    <t>As of 27-Aug-2026</t>
+    <t>As of 01-Sep-2026</t>
   </si>
   <si>
     <t>Name</t>
@@ -261,6 +261,18 @@
     <t>B7KH3G6</t>
   </si>
   <si>
+    <t>MICRON TECHNOLOGY INC</t>
+  </si>
+  <si>
+    <t>MU</t>
+  </si>
+  <si>
+    <t>595112103</t>
+  </si>
+  <si>
+    <t>2588184</t>
+  </si>
+  <si>
     <t>ADVANCED MICRO DEVICES</t>
   </si>
   <si>
@@ -273,18 +285,6 @@
     <t>2007849</t>
   </si>
   <si>
-    <t>MICRON TECHNOLOGY INC</t>
-  </si>
-  <si>
-    <t>MU</t>
-  </si>
-  <si>
-    <t>595112103</t>
-  </si>
-  <si>
-    <t>2588184</t>
-  </si>
-  <si>
     <t>QORVO INC</t>
   </si>
   <si>
@@ -297,6 +297,90 @@
     <t>BR9YYP4</t>
   </si>
   <si>
+    <t>SILICON LABORATORIES INC</t>
+  </si>
+  <si>
+    <t>SLAB</t>
+  </si>
+  <si>
+    <t>826919102</t>
+  </si>
+  <si>
+    <t>2568131</t>
+  </si>
+  <si>
+    <t>BROADCOM INC</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>11135F101</t>
+  </si>
+  <si>
+    <t>BDZ78H9</t>
+  </si>
+  <si>
+    <t>SKYWORKS SOLUTIONS INC</t>
+  </si>
+  <si>
+    <t>SWKS</t>
+  </si>
+  <si>
+    <t>83088M102</t>
+  </si>
+  <si>
+    <t>2961053</t>
+  </si>
+  <si>
+    <t>UNIVERSAL DISPLAY CORP</t>
+  </si>
+  <si>
+    <t>OLED</t>
+  </si>
+  <si>
+    <t>91347P105</t>
+  </si>
+  <si>
+    <t>2277880</t>
+  </si>
+  <si>
+    <t>ANALOG DEVICES INC</t>
+  </si>
+  <si>
+    <t>ADI</t>
+  </si>
+  <si>
+    <t>032654105</t>
+  </si>
+  <si>
+    <t>2032067</t>
+  </si>
+  <si>
+    <t>TEXAS INSTRUMENTS INC</t>
+  </si>
+  <si>
+    <t>TXN</t>
+  </si>
+  <si>
+    <t>882508104</t>
+  </si>
+  <si>
+    <t>2885409</t>
+  </si>
+  <si>
+    <t>QUALCOMM INC</t>
+  </si>
+  <si>
+    <t>QCOM</t>
+  </si>
+  <si>
+    <t>747525103</t>
+  </si>
+  <si>
+    <t>2714923</t>
+  </si>
+  <si>
     <t>CREDO TECHNOLOGY GROUP HOLDI</t>
   </si>
   <si>
@@ -309,52 +393,64 @@
     <t>BLD13F2</t>
   </si>
   <si>
-    <t>SILICON LABORATORIES INC</t>
-  </si>
-  <si>
-    <t>SLAB</t>
-  </si>
-  <si>
-    <t>826919102</t>
-  </si>
-  <si>
-    <t>2568131</t>
-  </si>
-  <si>
-    <t>BROADCOM INC</t>
-  </si>
-  <si>
-    <t>AVGO</t>
-  </si>
-  <si>
-    <t>11135F101</t>
-  </si>
-  <si>
-    <t>BDZ78H9</t>
-  </si>
-  <si>
-    <t>UNIVERSAL DISPLAY CORP</t>
-  </si>
-  <si>
-    <t>OLED</t>
-  </si>
-  <si>
-    <t>91347P105</t>
-  </si>
-  <si>
-    <t>2277880</t>
-  </si>
-  <si>
-    <t>SKYWORKS SOLUTIONS INC</t>
-  </si>
-  <si>
-    <t>SWKS</t>
-  </si>
-  <si>
-    <t>83088M102</t>
-  </si>
-  <si>
-    <t>2961053</t>
+    <t>DIODES INC</t>
+  </si>
+  <si>
+    <t>DIOD</t>
+  </si>
+  <si>
+    <t>254543101</t>
+  </si>
+  <si>
+    <t>2270500</t>
+  </si>
+  <si>
+    <t>SEMTECH CORP</t>
+  </si>
+  <si>
+    <t>SMTC</t>
+  </si>
+  <si>
+    <t>816850101</t>
+  </si>
+  <si>
+    <t>2795542</t>
+  </si>
+  <si>
+    <t>ASTERA LABS INC</t>
+  </si>
+  <si>
+    <t>ALAB</t>
+  </si>
+  <si>
+    <t>04626A103</t>
+  </si>
+  <si>
+    <t>BMTQ7V2</t>
+  </si>
+  <si>
+    <t>LATTICE SEMICONDUCTOR CORP</t>
+  </si>
+  <si>
+    <t>LSCC</t>
+  </si>
+  <si>
+    <t>518415104</t>
+  </si>
+  <si>
+    <t>2506658</t>
+  </si>
+  <si>
+    <t>MONOLITHIC POWER SYSTEMS INC</t>
+  </si>
+  <si>
+    <t>MPWR</t>
+  </si>
+  <si>
+    <t>609839105</t>
+  </si>
+  <si>
+    <t>B01Z7J1</t>
   </si>
   <si>
     <t>MARVELL TECHNOLOGY INC</t>
@@ -369,78 +465,6 @@
     <t>BNKJSM5</t>
   </si>
   <si>
-    <t>ANALOG DEVICES INC</t>
-  </si>
-  <si>
-    <t>ADI</t>
-  </si>
-  <si>
-    <t>032654105</t>
-  </si>
-  <si>
-    <t>2032067</t>
-  </si>
-  <si>
-    <t>TEXAS INSTRUMENTS INC</t>
-  </si>
-  <si>
-    <t>TXN</t>
-  </si>
-  <si>
-    <t>882508104</t>
-  </si>
-  <si>
-    <t>2885409</t>
-  </si>
-  <si>
-    <t>SEMTECH CORP</t>
-  </si>
-  <si>
-    <t>SMTC</t>
-  </si>
-  <si>
-    <t>816850101</t>
-  </si>
-  <si>
-    <t>2795542</t>
-  </si>
-  <si>
-    <t>ASTERA LABS INC</t>
-  </si>
-  <si>
-    <t>ALAB</t>
-  </si>
-  <si>
-    <t>04626A103</t>
-  </si>
-  <si>
-    <t>BMTQ7V2</t>
-  </si>
-  <si>
-    <t>LATTICE SEMICONDUCTOR CORP</t>
-  </si>
-  <si>
-    <t>LSCC</t>
-  </si>
-  <si>
-    <t>518415104</t>
-  </si>
-  <si>
-    <t>2506658</t>
-  </si>
-  <si>
-    <t>DIODES INC</t>
-  </si>
-  <si>
-    <t>DIOD</t>
-  </si>
-  <si>
-    <t>254543101</t>
-  </si>
-  <si>
-    <t>2270500</t>
-  </si>
-  <si>
     <t>SITIME CORP</t>
   </si>
   <si>
@@ -453,6 +477,18 @@
     <t>BKS48R6</t>
   </si>
   <si>
+    <t>INTEL CORP</t>
+  </si>
+  <si>
+    <t>INTC</t>
+  </si>
+  <si>
+    <t>458140100</t>
+  </si>
+  <si>
+    <t>2463247</t>
+  </si>
+  <si>
     <t>PENGUIN SOLUTIONS INC</t>
   </si>
   <si>
@@ -465,16 +501,28 @@
     <t>BRJHSZ1</t>
   </si>
   <si>
-    <t>MONOLITHIC POWER SYSTEMS INC</t>
-  </si>
-  <si>
-    <t>MPWR</t>
-  </si>
-  <si>
-    <t>609839105</t>
-  </si>
-  <si>
-    <t>B01Z7J1</t>
+    <t>MICROCHIP TECHNOLOGY INC</t>
+  </si>
+  <si>
+    <t>MCHP</t>
+  </si>
+  <si>
+    <t>595017104</t>
+  </si>
+  <si>
+    <t>2592174</t>
+  </si>
+  <si>
+    <t>FIRST SOLAR INC</t>
+  </si>
+  <si>
+    <t>FSLR</t>
+  </si>
+  <si>
+    <t>336433107</t>
+  </si>
+  <si>
+    <t>B1HMF22</t>
   </si>
   <si>
     <t>MAXLINEAR INC</t>
@@ -489,40 +537,28 @@
     <t>B3RDWC8</t>
   </si>
   <si>
-    <t>QUALCOMM INC</t>
-  </si>
-  <si>
-    <t>QCOM</t>
-  </si>
-  <si>
-    <t>747525103</t>
-  </si>
-  <si>
-    <t>2714923</t>
-  </si>
-  <si>
-    <t>INTEL CORP</t>
-  </si>
-  <si>
-    <t>INTC</t>
-  </si>
-  <si>
-    <t>458140100</t>
-  </si>
-  <si>
-    <t>2463247</t>
-  </si>
-  <si>
-    <t>MICROCHIP TECHNOLOGY INC</t>
-  </si>
-  <si>
-    <t>MCHP</t>
-  </si>
-  <si>
-    <t>595017104</t>
-  </si>
-  <si>
-    <t>2592174</t>
+    <t>ALLEGRO MICROSYSTEMS INC</t>
+  </si>
+  <si>
+    <t>ALGM</t>
+  </si>
+  <si>
+    <t>01749D105</t>
+  </si>
+  <si>
+    <t>BN4LSB6</t>
+  </si>
+  <si>
+    <t>NXP SEMICONDUCTORS NV</t>
+  </si>
+  <si>
+    <t>NXPI</t>
+  </si>
+  <si>
+    <t>N6596X109</t>
+  </si>
+  <si>
+    <t>B505PN7</t>
   </si>
   <si>
     <t>RIGETTI COMPUTING INC</t>
@@ -537,40 +573,28 @@
     <t>BN45WL6</t>
   </si>
   <si>
-    <t>ALLEGRO MICROSYSTEMS INC</t>
-  </si>
-  <si>
-    <t>ALGM</t>
-  </si>
-  <si>
-    <t>01749D105</t>
-  </si>
-  <si>
-    <t>BN4LSB6</t>
-  </si>
-  <si>
-    <t>FIRST SOLAR INC</t>
-  </si>
-  <si>
-    <t>FSLR</t>
-  </si>
-  <si>
-    <t>336433107</t>
-  </si>
-  <si>
-    <t>B1HMF22</t>
-  </si>
-  <si>
-    <t>NXP SEMICONDUCTORS NV</t>
-  </si>
-  <si>
-    <t>NXPI</t>
-  </si>
-  <si>
-    <t>N6596X109</t>
-  </si>
-  <si>
-    <t>B505PN7</t>
+    <t>MACOM TECHNOLOGY SOLUTIONS H</t>
+  </si>
+  <si>
+    <t>MTSI</t>
+  </si>
+  <si>
+    <t>55405Y100</t>
+  </si>
+  <si>
+    <t>B5B15Y5</t>
+  </si>
+  <si>
+    <t>SYNAPTICS INC</t>
+  </si>
+  <si>
+    <t>SYNA</t>
+  </si>
+  <si>
+    <t>87157D109</t>
+  </si>
+  <si>
+    <t>2839268</t>
   </si>
   <si>
     <t>CEREBRAS SYSTEMS INC   A</t>
@@ -585,28 +609,16 @@
     <t>BQ732F2</t>
   </si>
   <si>
-    <t>MACOM TECHNOLOGY SOLUTIONS H</t>
-  </si>
-  <si>
-    <t>MTSI</t>
-  </si>
-  <si>
-    <t>55405Y100</t>
-  </si>
-  <si>
-    <t>B5B15Y5</t>
-  </si>
-  <si>
-    <t>SYNAPTICS INC</t>
-  </si>
-  <si>
-    <t>SYNA</t>
-  </si>
-  <si>
-    <t>87157D109</t>
-  </si>
-  <si>
-    <t>2839268</t>
+    <t>CIRRUS LOGIC INC</t>
+  </si>
+  <si>
+    <t>CRUS</t>
+  </si>
+  <si>
+    <t>172755100</t>
+  </si>
+  <si>
+    <t>2197308</t>
   </si>
   <si>
     <t>POWER INTEGRATIONS INC</t>
@@ -621,16 +633,40 @@
     <t>2133045</t>
   </si>
   <si>
-    <t>CIRRUS LOGIC INC</t>
-  </si>
-  <si>
-    <t>CRUS</t>
-  </si>
-  <si>
-    <t>172755100</t>
-  </si>
-  <si>
-    <t>2197308</t>
+    <t>ON SEMICONDUCTOR</t>
+  </si>
+  <si>
+    <t>ON</t>
+  </si>
+  <si>
+    <t>682189105</t>
+  </si>
+  <si>
+    <t>2583576</t>
+  </si>
+  <si>
+    <t>RAMBUS INC</t>
+  </si>
+  <si>
+    <t>RMBS</t>
+  </si>
+  <si>
+    <t>750917106</t>
+  </si>
+  <si>
+    <t>2721967</t>
+  </si>
+  <si>
+    <t>WOLFSPEED INC</t>
+  </si>
+  <si>
+    <t>WOLF</t>
+  </si>
+  <si>
+    <t>97785W106</t>
+  </si>
+  <si>
+    <t>BVBFJH0</t>
   </si>
   <si>
     <t>INDIE SEMICONDUCTOR INC A</t>
@@ -645,30 +681,6 @@
     <t>BP4W0C8</t>
   </si>
   <si>
-    <t>ON SEMICONDUCTOR</t>
-  </si>
-  <si>
-    <t>ON</t>
-  </si>
-  <si>
-    <t>682189105</t>
-  </si>
-  <si>
-    <t>2583576</t>
-  </si>
-  <si>
-    <t>RAMBUS INC</t>
-  </si>
-  <si>
-    <t>RMBS</t>
-  </si>
-  <si>
-    <t>750917106</t>
-  </si>
-  <si>
-    <t>2721967</t>
-  </si>
-  <si>
     <t>T1 ENERGY INC</t>
   </si>
   <si>
@@ -681,18 +693,6 @@
     <t>BSKPBK7</t>
   </si>
   <si>
-    <t>WOLFSPEED INC</t>
-  </si>
-  <si>
-    <t>WOLF</t>
-  </si>
-  <si>
-    <t>97785W106</t>
-  </si>
-  <si>
-    <t>BVBFJH0</t>
-  </si>
-  <si>
     <t>NAVITAS SEMICONDUCTOR CORP</t>
   </si>
   <si>
@@ -783,6 +783,12 @@
     <t>924QSGII3</t>
   </si>
   <si>
+    <t>US DOLLAR</t>
+  </si>
+  <si>
+    <t>999USDZ92</t>
+  </si>
+  <si>
     <t>IONQ INC</t>
   </si>
   <si>
@@ -793,12 +799,6 @@
   </si>
   <si>
     <t>BP484B3</t>
-  </si>
-  <si>
-    <t>US DOLLAR</t>
-  </si>
-  <si>
-    <t>999USDZ92</t>
   </si>
 </sst>
 </file>
@@ -1647,13 +1647,13 @@
         <v>24</v>
       </c>
       <c r="E6" t="n" s="19">
-        <v>3.667908</v>
+        <v>3.882905</v>
       </c>
       <c r="F6" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G6" t="n" s="20">
-        <v>583858.0</v>
+        <v>581133.0</v>
       </c>
       <c r="H6" t="s" s="18">
         <v>26</v>
@@ -1673,13 +1673,13 @@
         <v>30</v>
       </c>
       <c r="E7" t="n" s="21">
-        <v>3.047053</v>
+        <v>3.074342</v>
       </c>
       <c r="F7" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G7" t="n" s="22">
-        <v>357571.0</v>
+        <v>355903.0</v>
       </c>
       <c r="H7" t="s" s="18">
         <v>26</v>
@@ -1699,13 +1699,13 @@
         <v>34</v>
       </c>
       <c r="E8" t="n" s="23">
-        <v>3.042401</v>
+        <v>3.067828</v>
       </c>
       <c r="F8" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G8" t="n" s="24">
-        <v>1143825.0</v>
+        <v>1138487.0</v>
       </c>
       <c r="H8" t="s" s="18">
         <v>26</v>
@@ -1725,13 +1725,13 @@
         <v>38</v>
       </c>
       <c r="E9" t="n" s="25">
-        <v>2.815648</v>
+        <v>2.957245</v>
       </c>
       <c r="F9" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G9" t="n" s="26">
-        <v>158030.0</v>
+        <v>79748.0</v>
       </c>
       <c r="H9" t="s" s="18">
         <v>26</v>
@@ -1751,13 +1751,13 @@
         <v>42</v>
       </c>
       <c r="E10" t="n" s="27">
-        <v>2.801373</v>
+        <v>2.871934</v>
       </c>
       <c r="F10" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G10" t="n" s="28">
-        <v>80123.0</v>
+        <v>157291.0</v>
       </c>
       <c r="H10" t="s" s="18">
         <v>26</v>
@@ -1777,13 +1777,13 @@
         <v>46</v>
       </c>
       <c r="E11" t="n" s="29">
-        <v>2.706226</v>
+        <v>2.869336</v>
       </c>
       <c r="F11" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G11" t="n" s="30">
-        <v>752763.0</v>
+        <v>749244.0</v>
       </c>
       <c r="H11" t="s" s="18">
         <v>26</v>
@@ -1803,13 +1803,13 @@
         <v>50</v>
       </c>
       <c r="E12" t="n" s="31">
-        <v>2.702127</v>
+        <v>2.844165</v>
       </c>
       <c r="F12" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G12" t="n" s="32">
-        <v>300912.0</v>
+        <v>326732.0</v>
       </c>
       <c r="H12" t="s" s="18">
         <v>26</v>
@@ -1829,13 +1829,13 @@
         <v>54</v>
       </c>
       <c r="E13" t="n" s="33">
-        <v>2.686531</v>
+        <v>2.808104</v>
       </c>
       <c r="F13" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G13" t="n" s="34">
-        <v>328266.0</v>
+        <v>191208.0</v>
       </c>
       <c r="H13" t="s" s="18">
         <v>26</v>
@@ -1855,13 +1855,13 @@
         <v>58</v>
       </c>
       <c r="E14" t="n" s="35">
-        <v>2.667887</v>
+        <v>2.711887</v>
       </c>
       <c r="F14" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G14" t="n" s="36">
-        <v>192106.0</v>
+        <v>1012666.0</v>
       </c>
       <c r="H14" t="s" s="18">
         <v>26</v>
@@ -1881,13 +1881,13 @@
         <v>62</v>
       </c>
       <c r="E15" t="n" s="37">
-        <v>2.595896</v>
+        <v>2.667134</v>
       </c>
       <c r="F15" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G15" t="n" s="38">
-        <v>818492.0</v>
+        <v>814674.0</v>
       </c>
       <c r="H15" t="s" s="18">
         <v>26</v>
@@ -1907,13 +1907,13 @@
         <v>66</v>
       </c>
       <c r="E16" t="n" s="39">
-        <v>2.561676</v>
+        <v>2.553039</v>
       </c>
       <c r="F16" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G16" t="n" s="40">
-        <v>1017422.0</v>
+        <v>181274.0</v>
       </c>
       <c r="H16" t="s" s="18">
         <v>26</v>
@@ -1933,13 +1933,13 @@
         <v>70</v>
       </c>
       <c r="E17" t="n" s="41">
-        <v>2.552898</v>
+        <v>2.54071</v>
       </c>
       <c r="F17" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G17" t="n" s="42">
-        <v>282869.0</v>
+        <v>252447.0</v>
       </c>
       <c r="H17" t="s" s="18">
         <v>26</v>
@@ -1959,13 +1959,13 @@
         <v>74</v>
       </c>
       <c r="E18" t="n" s="43">
-        <v>2.549562</v>
+        <v>2.464096</v>
       </c>
       <c r="F18" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G18" t="n" s="44">
-        <v>182125.0</v>
+        <v>372285.0</v>
       </c>
       <c r="H18" t="s" s="18">
         <v>26</v>
@@ -1985,13 +1985,13 @@
         <v>78</v>
       </c>
       <c r="E19" t="n" s="45">
-        <v>2.526896</v>
+        <v>2.458547</v>
       </c>
       <c r="F19" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G19" t="n" s="46">
-        <v>253632.0</v>
+        <v>299505.0</v>
       </c>
       <c r="H19" t="s" s="18">
         <v>26</v>
@@ -2011,13 +2011,13 @@
         <v>82</v>
       </c>
       <c r="E20" t="n" s="47">
-        <v>2.467703</v>
+        <v>2.452846</v>
       </c>
       <c r="F20" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G20" t="n" s="48">
-        <v>463522.0</v>
+        <v>708633.0</v>
       </c>
       <c r="H20" t="s" s="18">
         <v>26</v>
@@ -2037,13 +2037,13 @@
         <v>86</v>
       </c>
       <c r="E21" t="n" s="49">
-        <v>2.455428</v>
+        <v>2.424252</v>
       </c>
       <c r="F21" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G21" t="n" s="50">
-        <v>216025.0</v>
+        <v>461355.0</v>
       </c>
       <c r="H21" t="s" s="18">
         <v>26</v>
@@ -2063,13 +2063,13 @@
         <v>90</v>
       </c>
       <c r="E22" t="n" s="51">
-        <v>2.431235</v>
+        <v>2.390938</v>
       </c>
       <c r="F22" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G22" t="n" s="52">
-        <v>539917.0</v>
+        <v>215015.0</v>
       </c>
       <c r="H22" t="s" s="18">
         <v>26</v>
@@ -2089,13 +2089,13 @@
         <v>94</v>
       </c>
       <c r="E23" t="n" s="53">
-        <v>2.417964</v>
+        <v>2.384223</v>
       </c>
       <c r="F23" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G23" t="n" s="54">
-        <v>711961.0</v>
+        <v>537391.0</v>
       </c>
       <c r="H23" t="s" s="18">
         <v>26</v>
@@ -2115,13 +2115,13 @@
         <v>98</v>
       </c>
       <c r="E24" t="n" s="55">
-        <v>2.414099</v>
+        <v>2.353289</v>
       </c>
       <c r="F24" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G24" t="n" s="56">
-        <v>107662.0</v>
+        <v>48319.0</v>
       </c>
       <c r="H24" t="s" s="18">
         <v>26</v>
@@ -2141,13 +2141,13 @@
         <v>102</v>
       </c>
       <c r="E25" t="n" s="57">
-        <v>2.395798</v>
+        <v>2.353174</v>
       </c>
       <c r="F25" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G25" t="n" s="58">
-        <v>1222035.0</v>
+        <v>281545.0</v>
       </c>
       <c r="H25" t="s" s="18">
         <v>26</v>
@@ -2167,13 +2167,13 @@
         <v>106</v>
       </c>
       <c r="E26" t="n" s="59">
-        <v>2.37905</v>
+        <v>2.35309</v>
       </c>
       <c r="F26" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G26" t="n" s="60">
-        <v>48546.0</v>
+        <v>107159.0</v>
       </c>
       <c r="H26" t="s" s="18">
         <v>26</v>
@@ -2193,13 +2193,13 @@
         <v>110</v>
       </c>
       <c r="E27" t="n" s="61">
-        <v>2.356103</v>
+        <v>2.350283</v>
       </c>
       <c r="F27" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G27" t="n" s="62">
-        <v>993910.0</v>
+        <v>664960.0</v>
       </c>
       <c r="H27" t="s" s="18">
         <v>26</v>
@@ -2219,13 +2219,13 @@
         <v>114</v>
       </c>
       <c r="E28" t="n" s="63">
-        <v>2.30375</v>
+        <v>2.299563</v>
       </c>
       <c r="F28" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G28" t="n" s="64">
-        <v>374033.0</v>
+        <v>1216322.0</v>
       </c>
       <c r="H28" t="s" s="18">
         <v>26</v>
@@ -2245,13 +2245,13 @@
         <v>118</v>
       </c>
       <c r="E29" t="n" s="65">
-        <v>2.299661</v>
+        <v>2.297071</v>
       </c>
       <c r="F29" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G29" t="n" s="66">
-        <v>668083.0</v>
+        <v>809719.0</v>
       </c>
       <c r="H29" t="s" s="18">
         <v>26</v>
@@ -2271,13 +2271,13 @@
         <v>122</v>
       </c>
       <c r="E30" t="n" s="67">
-        <v>2.295513</v>
+        <v>2.264822</v>
       </c>
       <c r="F30" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G30" t="n" s="68">
-        <v>813522.0</v>
+        <v>285551.0</v>
       </c>
       <c r="H30" t="s" s="18">
         <v>26</v>
@@ -2297,13 +2297,13 @@
         <v>126</v>
       </c>
       <c r="E31" t="n" s="69">
-        <v>2.259979</v>
+        <v>2.263291</v>
       </c>
       <c r="F31" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G31" t="n" s="70">
-        <v>3677745.0</v>
+        <v>989264.0</v>
       </c>
       <c r="H31" t="s" s="18">
         <v>26</v>
@@ -2323,13 +2323,13 @@
         <v>130</v>
       </c>
       <c r="E32" t="n" s="71">
-        <v>2.255908</v>
+        <v>2.251829</v>
       </c>
       <c r="F32" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G32" t="n" s="72">
-        <v>1605566.0</v>
+        <v>1598060.0</v>
       </c>
       <c r="H32" t="s" s="18">
         <v>26</v>
@@ -2349,13 +2349,13 @@
         <v>134</v>
       </c>
       <c r="E33" t="n" s="73">
-        <v>2.253022</v>
+        <v>2.202189</v>
       </c>
       <c r="F33" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G33" t="n" s="74">
-        <v>286892.0</v>
+        <v>249252.0</v>
       </c>
       <c r="H33" t="s" s="18">
         <v>26</v>
@@ -2375,13 +2375,13 @@
         <v>138</v>
       </c>
       <c r="E34" t="n" s="75">
-        <v>2.114144</v>
+        <v>2.179864</v>
       </c>
       <c r="F34" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G34" t="n" s="76">
-        <v>250423.0</v>
+        <v>3660553.0</v>
       </c>
       <c r="H34" t="s" s="18">
         <v>26</v>
@@ -2401,13 +2401,13 @@
         <v>142</v>
       </c>
       <c r="E35" t="n" s="77">
-        <v>2.102746</v>
+        <v>2.090901</v>
       </c>
       <c r="F35" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G35" t="n" s="78">
-        <v>301364.0</v>
+        <v>200879.0</v>
       </c>
       <c r="H35" t="s" s="18">
         <v>26</v>
@@ -2427,13 +2427,13 @@
         <v>146</v>
       </c>
       <c r="E36" t="n" s="79">
-        <v>2.090761</v>
+        <v>2.088974</v>
       </c>
       <c r="F36" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G36" t="n" s="80">
-        <v>201822.0</v>
+        <v>552525.0</v>
       </c>
       <c r="H36" t="s" s="18">
         <v>26</v>
@@ -2453,13 +2453,13 @@
         <v>150</v>
       </c>
       <c r="E37" t="n" s="81">
-        <v>2.024945</v>
+        <v>2.056972</v>
       </c>
       <c r="F37" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G37" t="n" s="82">
-        <v>555120.0</v>
+        <v>299955.0</v>
       </c>
       <c r="H37" t="s" s="18">
         <v>26</v>
@@ -2479,13 +2479,13 @@
         <v>154</v>
       </c>
       <c r="E38" t="n" s="83">
-        <v>1.980956</v>
+        <v>1.95374</v>
       </c>
       <c r="F38" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G38" t="n" s="84">
-        <v>958187.0</v>
+        <v>450900.0</v>
       </c>
       <c r="H38" t="s" s="18">
         <v>26</v>
@@ -2505,13 +2505,13 @@
         <v>158</v>
       </c>
       <c r="E39" t="n" s="85">
-        <v>1.877542</v>
+        <v>1.886042</v>
       </c>
       <c r="F39" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G39" t="n" s="86">
-        <v>453018.0</v>
+        <v>953708.0</v>
       </c>
       <c r="H39" t="s" s="18">
         <v>26</v>
@@ -2531,13 +2531,13 @@
         <v>162</v>
       </c>
       <c r="E40" t="n" s="87">
-        <v>1.819117</v>
+        <v>1.864758</v>
       </c>
       <c r="F40" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G40" t="n" s="88">
-        <v>1.2046425E7</v>
+        <v>646109.0</v>
       </c>
       <c r="H40" t="s" s="18">
         <v>26</v>
@@ -2557,13 +2557,13 @@
         <v>166</v>
       </c>
       <c r="E41" t="n" s="89">
-        <v>1.814943</v>
+        <v>1.727862</v>
       </c>
       <c r="F41" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G41" t="n" s="90">
-        <v>649143.0</v>
+        <v>515330.0</v>
       </c>
       <c r="H41" t="s" s="18">
         <v>26</v>
@@ -2583,13 +2583,13 @@
         <v>170</v>
       </c>
       <c r="E42" t="n" s="91">
-        <v>1.763223</v>
+        <v>1.713466</v>
       </c>
       <c r="F42" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G42" t="n" s="92">
-        <v>517750.0</v>
+        <v>1639357.0</v>
       </c>
       <c r="H42" t="s" s="18">
         <v>26</v>
@@ -2609,13 +2609,13 @@
         <v>174</v>
       </c>
       <c r="E43" t="n" s="93">
-        <v>1.715182</v>
+        <v>1.690958</v>
       </c>
       <c r="F43" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G43" t="n" s="94">
-        <v>9251404.0</v>
+        <v>1.1990112E7</v>
       </c>
       <c r="H43" t="s" s="18">
         <v>26</v>
@@ -2635,13 +2635,13 @@
         <v>178</v>
       </c>
       <c r="E44" t="n" s="95">
-        <v>1.659159</v>
+        <v>1.56566</v>
       </c>
       <c r="F44" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G44" t="n" s="96">
-        <v>1647056.0</v>
+        <v>9208156.0</v>
       </c>
       <c r="H44" t="s" s="18">
         <v>26</v>
@@ -2661,13 +2661,13 @@
         <v>182</v>
       </c>
       <c r="E45" t="n" s="97">
-        <v>1.631232</v>
+        <v>1.509041</v>
       </c>
       <c r="F45" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G45" t="n" s="98">
-        <v>3488489.0</v>
+        <v>3472182.0</v>
       </c>
       <c r="H45" t="s" s="18">
         <v>26</v>
@@ -2687,13 +2687,13 @@
         <v>186</v>
       </c>
       <c r="E46" t="n" s="99">
-        <v>1.575717</v>
+        <v>1.455923</v>
       </c>
       <c r="F46" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G46" t="n" s="100">
-        <v>8746012.0</v>
+        <v>8705127.0</v>
       </c>
       <c r="H46" t="s" s="18">
         <v>26</v>
@@ -2713,13 +2713,13 @@
         <v>190</v>
       </c>
       <c r="E47" t="n" s="101">
-        <v>1.316182</v>
+        <v>1.254846</v>
       </c>
       <c r="F47" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G47" t="n" s="102">
-        <v>1342446.0</v>
+        <v>1336170.0</v>
       </c>
       <c r="H47" t="s" s="18">
         <v>26</v>
@@ -2739,13 +2739,13 @@
         <v>194</v>
       </c>
       <c r="E48" t="n" s="103">
-        <v>0.773081</v>
+        <v>0.761326</v>
       </c>
       <c r="F48" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G48" t="n" s="104">
-        <v>344193.0</v>
+        <v>342584.0</v>
       </c>
       <c r="H48" t="s" s="18">
         <v>26</v>
@@ -2765,13 +2765,13 @@
         <v>198</v>
       </c>
       <c r="E49" t="n" s="105">
-        <v>0.72831</v>
+        <v>0.711076</v>
       </c>
       <c r="F49" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G49" t="n" s="106">
-        <v>685601.0</v>
+        <v>682396.0</v>
       </c>
       <c r="H49" t="s" s="18">
         <v>26</v>
@@ -2791,13 +2791,13 @@
         <v>202</v>
       </c>
       <c r="E50" t="n" s="107">
-        <v>0.568195</v>
+        <v>0.545986</v>
       </c>
       <c r="F50" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G50" t="n" s="108">
-        <v>870627.0</v>
+        <v>866557.0</v>
       </c>
       <c r="H50" t="s" s="18">
         <v>26</v>
@@ -2817,13 +2817,13 @@
         <v>206</v>
       </c>
       <c r="E51" t="n" s="109">
-        <v>0.518746</v>
+        <v>0.501147</v>
       </c>
       <c r="F51" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G51" t="n" s="110">
-        <v>129606.0</v>
+        <v>129000.0</v>
       </c>
       <c r="H51" t="s" s="18">
         <v>26</v>
@@ -2843,13 +2843,13 @@
         <v>25</v>
       </c>
       <c r="E52" t="n" s="111">
-        <v>0.019113</v>
+        <v>0.025524</v>
       </c>
       <c r="F52" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G52" t="n" s="112">
-        <v>511332.15</v>
+        <v>642484.68</v>
       </c>
       <c r="H52" t="s" s="18">
         <v>26</v>
@@ -2860,22 +2860,22 @@
         <v>209</v>
       </c>
       <c r="B53" t="s" s="18">
+        <v>25</v>
+      </c>
+      <c r="C53" t="s" s="18">
         <v>210</v>
       </c>
-      <c r="C53" t="s" s="18">
-        <v>211</v>
-      </c>
       <c r="D53" t="s" s="18">
-        <v>212</v>
+        <v>25</v>
       </c>
       <c r="E53" t="n" s="113">
-        <v>2.0E-6</v>
+        <v>2.56E-4</v>
       </c>
       <c r="F53" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G53" t="n" s="114">
-        <v>1.0</v>
+        <v>6434.2</v>
       </c>
       <c r="H53" t="s" s="18">
         <v>26</v>
@@ -2883,25 +2883,25 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="18">
+        <v>211</v>
+      </c>
+      <c r="B54" t="s" s="18">
+        <v>212</v>
+      </c>
+      <c r="C54" t="s" s="18">
         <v>213</v>
       </c>
-      <c r="B54" t="s" s="18">
-        <v>25</v>
-      </c>
-      <c r="C54" t="s" s="18">
+      <c r="D54" t="s" s="18">
         <v>214</v>
       </c>
-      <c r="D54" t="s" s="18">
-        <v>25</v>
-      </c>
       <c r="E54" t="n" s="115">
-        <v>-2.0E-5</v>
+        <v>2.0E-6</v>
       </c>
       <c r="F54" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G54" t="n" s="116">
-        <v>-546.47</v>
+        <v>1.0</v>
       </c>
       <c r="H54" t="s" s="18">
         <v>26</v>
